--- a/utils/monday_sprint_sprint_2024-39.xlsx
+++ b/utils/monday_sprint_sprint_2024-39.xlsx
@@ -3455,7 +3455,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>25</v>
@@ -3469,7 +3469,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>32</v>
@@ -3483,7 +3483,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>33</v>
@@ -3497,7 +3497,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>36</v>

--- a/utils/monday_sprint_sprint_2024-39.xlsx
+++ b/utils/monday_sprint_sprint_2024-39.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="185">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>26499</t>
+    <t>6884019017</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>21/06/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>26/06/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -129,6 +129,9 @@
     <t>19/02/2024</t>
   </si>
   <si>
+    <t>04/07/2024</t>
+  </si>
+  <si>
     <t>Fevereiro</t>
   </si>
   <si>
@@ -144,7 +147,7 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>26087</t>
+    <t>6891514186</t>
   </si>
   <si>
     <t>WMS Almoxarifado - Preparação ambiente WEB</t>
@@ -153,22 +156,28 @@
     <t>24/06/2024</t>
   </si>
   <si>
+    <t>02/07/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Enviar para os demais analistas os parâmetros de controle de caixa</t>
   </si>
   <si>
-    <t>26568</t>
+    <t>6883870744</t>
   </si>
   <si>
     <t>Certificado da qualidade só aparecer ensaios aprovados</t>
   </si>
   <si>
+    <t>06/07/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>6920730920</t>
   </si>
   <si>
     <t>Criar Estrutura de Três níveis de GRID de consulta na Tela de Gestão Avista dos Eventos de Pagamento</t>
@@ -177,15 +186,33 @@
     <t>27/06/2024</t>
   </si>
   <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>6920749418</t>
+  </si>
+  <si>
     <t>Inclusão de Novos Filtros na Tela de Gestão e automação da Carga dos Grids</t>
   </si>
   <si>
+    <t>6920758168</t>
+  </si>
+  <si>
     <t>Criar processo de Geração Automática das Parcelas na tela de Geração de Eventos de Pagamento, para  parcelas por Quantidade de Peças (Lote</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>6920773226</t>
+  </si>
+  <si>
     <t>Criar Estrutura de Dados (Tabelas Oracle) para gravar os dados de Integração do Benner durante validação</t>
   </si>
   <si>
+    <t>6973894003</t>
+  </si>
+  <si>
     <t>Criar consulta dos titulos a serem integrados com o Benner</t>
   </si>
   <si>
@@ -198,7 +225,7 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>24542</t>
+    <t>6715094571</t>
   </si>
   <si>
     <t>Plano de ação WMS - OM</t>
@@ -207,10 +234,13 @@
     <t>27/05/2024</t>
   </si>
   <si>
+    <t>08/07/2024</t>
+  </si>
+  <si>
     <t>Maio</t>
   </si>
   <si>
-    <t>26272</t>
+    <t>6794444599</t>
   </si>
   <si>
     <t>[Compras | NIMBI] Liberação Campo Almoxarifado E Sub-Grupos</t>
@@ -219,7 +249,7 @@
     <t>07/06/2024</t>
   </si>
   <si>
-    <t>26466</t>
+    <t>6846453021</t>
   </si>
   <si>
     <t>ALTERAR A ROTINA PARA QUE A MENSAGEM DE RETORNO DE ESTOURO DE VERBA TRAGA O CENTRO DE CUSTO</t>
@@ -228,19 +258,22 @@
     <t>17/06/2024</t>
   </si>
   <si>
-    <t>26596</t>
+    <t>6883757194</t>
   </si>
   <si>
     <t>QUANTIDADE FATURAMENTO FERRAMENTAL</t>
   </si>
   <si>
-    <t>26494</t>
+    <t>6884073228</t>
   </si>
   <si>
     <t>ANEXOS DO CPP</t>
   </si>
   <si>
-    <t>26492</t>
+    <t>25/06/2024</t>
+  </si>
+  <si>
+    <t>6884080526</t>
   </si>
   <si>
     <t>Correção</t>
@@ -249,31 +282,31 @@
     <t>Problemas no sistema fiscal</t>
   </si>
   <si>
-    <t>26411</t>
+    <t>6884177192</t>
   </si>
   <si>
     <t>[COMPRAS] Criar botão para acelerar a devolução dos pedidos</t>
   </si>
   <si>
-    <t>26392</t>
+    <t>6884193617</t>
   </si>
   <si>
     <t>Consertos do sistema de modelos</t>
   </si>
   <si>
-    <t>26387</t>
+    <t>6884205674</t>
   </si>
   <si>
     <t>LIGAS MODELO/SERVIÇOS/DISPOSITIVOS</t>
   </si>
   <si>
-    <t>26349</t>
+    <t>6884218754</t>
   </si>
   <si>
     <t>Consulta por material na pré-lista</t>
   </si>
   <si>
-    <t>26357</t>
+    <t>6806999367</t>
   </si>
   <si>
     <t>Workflow fechamento de materiais - Análise</t>
@@ -282,157 +315,157 @@
     <t>10/06/2024</t>
   </si>
   <si>
-    <t>26617</t>
+    <t>6884640688</t>
   </si>
   <si>
     <t>Ocultar o botão tela de pré-lista almoxarifado</t>
   </si>
   <si>
-    <t>26329</t>
+    <t>6891518996</t>
   </si>
   <si>
     <t>Sistema Solicitação de Embalagens / Inventário de Embalagens</t>
   </si>
   <si>
-    <t>26606</t>
+    <t>6896156555</t>
   </si>
   <si>
     <t>TELA CADASTRO DE ENDEREÇO - ALMOXARIFADO</t>
   </si>
   <si>
-    <t>26598</t>
+    <t>6883747635</t>
   </si>
   <si>
     <t>Relatório - Dispositivo e Ferramenta de Usinagem</t>
   </si>
   <si>
-    <t>26608</t>
+    <t>6883735943</t>
   </si>
   <si>
     <t>Ajustar as informações na tela de carregamento</t>
   </si>
   <si>
-    <t>26502</t>
+    <t>6883996714</t>
   </si>
   <si>
     <t>Ajuste no relatório GESTÃO DE ESTOQUES</t>
   </si>
   <si>
-    <t>26467</t>
+    <t>6884099079</t>
   </si>
   <si>
     <t>Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>26590</t>
-  </si>
-  <si>
-    <t>26570</t>
+    <t>6883789927</t>
+  </si>
+  <si>
+    <t>6883862249</t>
   </si>
   <si>
     <t>SITUAÇÃO DEPOSITO</t>
   </si>
   <si>
-    <t>26026</t>
+    <t>6891457325</t>
   </si>
   <si>
     <t>AJUSTE ETIQUETA E INVOICE - LINES DA ORDEM DE COMPRA</t>
   </si>
   <si>
-    <t>26495</t>
+    <t>6884067351</t>
   </si>
   <si>
     <t>Pré-roteiro AP-119</t>
   </si>
   <si>
-    <t>26572</t>
+    <t>6883816931</t>
   </si>
   <si>
     <t>Consulta saldo de conjunto</t>
   </si>
   <si>
-    <t>26436</t>
+    <t>6884122859</t>
   </si>
   <si>
     <t>Adicionar Pergunta na MPO - Usinagem</t>
   </si>
   <si>
-    <t>26463</t>
+    <t>6884118452</t>
   </si>
   <si>
     <t>Alteração do apontamento ajustagem</t>
   </si>
   <si>
-    <t>26400</t>
+    <t>6884182909</t>
   </si>
   <si>
     <t>Sequência sem cadastro - Irog</t>
   </si>
   <si>
-    <t>26415</t>
+    <t>6884171787</t>
   </si>
   <si>
     <t>Atualização revisão do modelo - Irog</t>
   </si>
   <si>
-    <t>26360</t>
+    <t>6884211862</t>
   </si>
   <si>
     <t>Data contratual</t>
   </si>
   <si>
-    <t>26537</t>
+    <t>6883907858</t>
   </si>
   <si>
     <t>Melhoria Sistema PCP - Relatórios Estatísticas Mensais (Movimentação) - Entradas No Depósito</t>
   </si>
   <si>
-    <t>26552</t>
+    <t>6883899494</t>
   </si>
   <si>
     <t>Apontamento Ajustagem / Pintura</t>
   </si>
   <si>
-    <t>26536</t>
+    <t>6883916496</t>
   </si>
   <si>
     <t>Melhoria Sistema PCP - Relatórios Estatísticas Mensais (Movimentação) - Entradas Na Usinagem</t>
   </si>
   <si>
-    <t>26656</t>
+    <t>6901457999</t>
   </si>
   <si>
     <t>INATIVAR SETOR 548</t>
   </si>
   <si>
-    <t>25/06/2024</t>
-  </si>
-  <si>
-    <t>26593</t>
+    <t>6883769542</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DOS FLUXOS</t>
   </si>
   <si>
-    <t>26418</t>
+    <t>11/07/2024</t>
+  </si>
+  <si>
+    <t>6884157529</t>
   </si>
   <si>
     <t>Exclusão Única</t>
   </si>
   <si>
-    <t>26425</t>
+    <t>6884146341</t>
   </si>
   <si>
     <t>Apontamento de Inspeção</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>6891432855</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
   </si>
   <si>
-    <t>26514</t>
+    <t>6883931851</t>
   </si>
   <si>
     <t>Melhoria Sistema Refugo/Estorno Peça não Vazada</t>
@@ -444,7 +477,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-39</t>
+    <t>Fev/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -514,6 +547,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1092,7 +1128,7 @@
         <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1104,7 +1140,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1121,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>34</v>
@@ -1151,7 +1187,7 @@
         <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1168,7 +1204,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
@@ -1183,7 +1219,7 @@
         <v>36</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1195,7 +1231,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1203,7 +1239,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1215,10 +1251,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1230,10 +1266,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1242,7 +1278,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1262,7 +1298,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>34</v>
@@ -1277,10 +1313,10 @@
         <v>36</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1289,7 +1325,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1297,7 +1333,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1309,10 +1345,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1327,10 +1363,10 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>26</v>
@@ -1344,7 +1380,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1356,10 +1392,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1371,10 +1407,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1383,7 +1419,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1391,7 +1427,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1403,10 +1439,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1418,10 +1454,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1430,7 +1466,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1438,7 +1474,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1450,10 +1486,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1465,10 +1501,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1477,7 +1513,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1485,7 +1521,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1497,25 +1533,25 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1524,7 +1560,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1532,7 +1568,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1544,10 +1580,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1559,10 +1595,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1571,15 +1607,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1591,10 +1627,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1606,10 +1642,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1618,15 +1654,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1638,10 +1674,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1653,10 +1689,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1665,7 +1701,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1673,7 +1709,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1685,10 +1721,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1700,10 +1736,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1720,7 +1756,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1732,10 +1768,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1750,7 +1786,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1767,7 +1803,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1779,10 +1815,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1797,7 +1833,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1814,22 +1850,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1861,7 +1897,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1873,10 +1909,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1891,7 +1927,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1908,7 +1944,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1920,10 +1956,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1955,7 +1991,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1967,10 +2003,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1985,7 +2021,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2002,7 +2038,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2014,10 +2050,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2049,7 +2085,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2061,10 +2097,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2076,10 +2112,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2088,7 +2124,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2096,22 +2132,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2126,7 +2162,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2143,7 +2179,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2155,10 +2191,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2170,7 +2206,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2182,7 +2218,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2190,7 +2226,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2202,10 +2238,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2217,10 +2253,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2229,7 +2265,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2237,7 +2273,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2249,10 +2285,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2267,7 +2303,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2284,7 +2320,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2296,10 +2332,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2314,7 +2350,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2331,7 +2367,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2343,10 +2379,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2361,7 +2397,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2378,7 +2414,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2390,10 +2426,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2408,7 +2444,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2425,7 +2461,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2437,10 +2473,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2455,7 +2491,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2472,7 +2508,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2484,10 +2520,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2502,7 +2538,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2519,7 +2555,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2531,10 +2567,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2546,10 +2582,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2558,7 +2594,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2566,7 +2602,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2578,10 +2614,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2596,7 +2632,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2613,7 +2649,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2625,10 +2661,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2643,7 +2679,7 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2660,7 +2696,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2672,10 +2708,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2690,7 +2726,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2707,7 +2743,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2719,10 +2755,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2737,7 +2773,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2754,7 +2790,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2766,10 +2802,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2784,7 +2820,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2801,7 +2837,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2813,10 +2849,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2831,7 +2867,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2848,7 +2884,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2860,10 +2896,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2878,7 +2914,7 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2895,7 +2931,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2907,10 +2943,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2925,7 +2961,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2942,7 +2978,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2954,10 +2990,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2972,7 +3008,7 @@
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2989,7 +3025,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3001,10 +3037,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3019,7 +3055,7 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3036,7 +3072,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3048,10 +3084,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3063,10 +3099,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3075,7 +3111,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3083,7 +3119,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3095,10 +3131,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3113,7 +3149,7 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3130,7 +3166,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3142,10 +3178,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3160,10 +3196,10 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>26</v>
@@ -3177,7 +3213,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3189,10 +3225,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3210,7 +3246,7 @@
         <v>24</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>26</v>
@@ -3224,7 +3260,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3236,10 +3272,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3251,19 +3287,19 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3271,7 +3307,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3283,10 +3319,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3304,7 +3340,7 @@
         <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>26</v>
@@ -3329,23 +3365,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3353,16 +3389,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3373,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>15.57</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -3381,7 +3417,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3394,7 +3430,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -3402,7 +3438,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3433,12 +3469,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B2">
         <v>49</v>
@@ -3452,7 +3488,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3462,25 +3498,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3497,13 +3533,13 @@
         <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3515,10 +3551,10 @@
         <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3535,7 +3571,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3547,21 +3583,21 @@
         <v>49</v>
       </c>
       <c r="M11" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3573,53 +3609,53 @@
         <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q12">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Q13">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -3627,7 +3663,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3635,7 +3671,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3643,7 +3679,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3651,10 +3687,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3662,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3670,142 +3706,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
